--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run5/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7320,0.0858,0.0518,0.1333</t>
-  </si>
-  <si>
-    <t>0.0134,0.0057,0.0010,0.9933</t>
-  </si>
-  <si>
-    <t>0.6643,0.0217,0.0220,0.3408</t>
-  </si>
-  <si>
-    <t>0.0297,0.0190,0.0023,0.9846</t>
-  </si>
-  <si>
-    <t>0.9891,0.0053,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9878,0.0085,0.0017,0.0009</t>
-  </si>
-  <si>
-    <t>0.9902,0.0057,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9897,0.0039,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9902,0.0043,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9922,0.0053,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9863,0.0094,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.9876,0.0066,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.4908,0.0904,0.5009,0.0299</t>
-  </si>
-  <si>
-    <t>0.3375,0.0571,0.6880,0.0191</t>
-  </si>
-  <si>
-    <t>0.1199,0.0132,0.9261,0.0030</t>
-  </si>
-  <si>
-    <t>0.1425,0.0666,0.8328,0.0101</t>
-  </si>
-  <si>
-    <t>0.4597,0.0513,0.6158,0.0188</t>
-  </si>
-  <si>
-    <t>0.0192,0.9656,0.0350,0.0011</t>
-  </si>
-  <si>
-    <t>0.0790,0.9328,0.0177,0.0010</t>
-  </si>
-  <si>
-    <t>0.1025,0.8997,0.0222,0.0016</t>
-  </si>
-  <si>
-    <t>0.0392,0.9484,0.0363,0.0009</t>
-  </si>
-  <si>
-    <t>0.0742,0.9250,0.0267,0.0018</t>
-  </si>
-  <si>
-    <t>0.4269,0.0738,0.5041,0.0821</t>
-  </si>
-  <si>
-    <t>0.4373,0.1999,0.4085,0.0864</t>
-  </si>
-  <si>
-    <t>0.0893,0.0066,0.8663,0.0597</t>
-  </si>
-  <si>
-    <t>0.0955,0.0482,0.8748,0.0182</t>
-  </si>
-  <si>
-    <t>0.0935,0.0104,0.9020,0.0302</t>
-  </si>
-  <si>
-    <t>0.1865,0.0217,0.7107,0.0857</t>
-  </si>
-  <si>
-    <t>0.0102,0.0029,0.9746,0.0240</t>
-  </si>
-  <si>
-    <t>0.4280,0.4774,0.0883,0.0053</t>
-  </si>
-  <si>
-    <t>0.6205,0.0626,0.3963,0.0221</t>
-  </si>
-  <si>
-    <t>0.0072,0.0202,0.9766,0.0150</t>
-  </si>
-  <si>
-    <t>0.0473,0.8906,0.1322,0.0069</t>
-  </si>
-  <si>
-    <t>0.7955,0.0632,0.0427,0.1108</t>
-  </si>
-  <si>
-    <t>0.6062,0.3189,0.1152,0.0149</t>
-  </si>
-  <si>
-    <t>0.8622,0.2194,0.0131,0.0025</t>
-  </si>
-  <si>
-    <t>0.0657,0.8655,0.1339,0.0023</t>
-  </si>
-  <si>
-    <t>0.0107,0.7019,0.7606,0.0051</t>
-  </si>
-  <si>
-    <t>0.0869,0.1431,0.7969,0.0404</t>
-  </si>
-  <si>
-    <t>0.0772,0.2670,0.7376,0.0291</t>
-  </si>
-  <si>
-    <t>0.1670,0.0193,0.2437,0.6001</t>
-  </si>
-  <si>
-    <t>0.0517,0.1350,0.8829,0.0123</t>
-  </si>
-  <si>
-    <t>0.0018,0.9739,0.3488,0.0007</t>
-  </si>
-  <si>
-    <t>0.0707,0.0668,0.8746,0.0127</t>
-  </si>
-  <si>
-    <t>0.1289,0.6834,0.0471,0.3223</t>
-  </si>
-  <si>
-    <t>0.0045,0.9818,0.0235,0.0049</t>
-  </si>
-  <si>
-    <t>0.0060,0.9535,0.3405,0.0009</t>
-  </si>
-  <si>
-    <t>0.0024,0.9858,0.1046,0.0011</t>
-  </si>
-  <si>
-    <t>0.0027,0.3012,0.9644,0.0022</t>
-  </si>
-  <si>
-    <t>0.0011,0.3403,0.9762,0.0008</t>
-  </si>
-  <si>
-    <t>0.1915,0.0484,0.8274,0.0084</t>
-  </si>
-  <si>
-    <t>0.1304,0.0095,0.8876,0.0179</t>
-  </si>
-  <si>
-    <t>0.0025,0.0107,0.9914,0.0033</t>
-  </si>
-  <si>
-    <t>0.0381,0.0324,0.9440,0.0097</t>
-  </si>
-  <si>
-    <t>0.9616,0.0456,0.0074,0.0017</t>
-  </si>
-  <si>
-    <t>0.9391,0.0891,0.0089,0.0014</t>
-  </si>
-  <si>
-    <t>0.9552,0.0332,0.0136,0.0037</t>
-  </si>
-  <si>
-    <t>0.0076,0.0991,0.9754,0.0017</t>
-  </si>
-  <si>
-    <t>0.9913,0.0023,0.0006,0.0020</t>
-  </si>
-  <si>
-    <t>0.9860,0.0112,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9304,0.1089,0.0089,0.0022</t>
-  </si>
-  <si>
-    <t>0.0019,0.8770,0.8428,0.0009</t>
-  </si>
-  <si>
-    <t>0.0064,0.0139,0.9794,0.0070</t>
-  </si>
-  <si>
-    <t>0.0128,0.2124,0.8960,0.0240</t>
-  </si>
-  <si>
-    <t>0.0027,0.8210,0.8598,0.0017</t>
-  </si>
-  <si>
-    <t>0.0045,0.0108,0.9805,0.0084</t>
-  </si>
-  <si>
-    <t>0.0120,0.9733,0.0409,0.0013</t>
-  </si>
-  <si>
-    <t>0.0030,0.9930,0.0184,0.0001</t>
-  </si>
-  <si>
-    <t>0.7280,0.0793,0.2597,0.0229</t>
-  </si>
-  <si>
-    <t>0.5467,0.2807,0.2223,0.0093</t>
-  </si>
-  <si>
-    <t>0.0186,0.0948,0.9480,0.0043</t>
-  </si>
-  <si>
-    <t>0.0018,0.8411,0.8380,0.0004</t>
-  </si>
-  <si>
-    <t>0.0017,0.7756,0.8937,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9868,0.2635,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.9298,0.8087,0.0002</t>
-  </si>
-  <si>
-    <t>0.0208,0.0042,0.0024,0.9894</t>
-  </si>
-  <si>
-    <t>0.0051,0.0105,0.0008,0.9958</t>
-  </si>
-  <si>
-    <t>0.0018,0.0210,0.0003,0.9979</t>
-  </si>
-  <si>
-    <t>0.0233,0.0075,0.0007,0.9912</t>
-  </si>
-  <si>
-    <t>0.0093,0.0071,0.0007,0.9949</t>
-  </si>
-  <si>
-    <t>0.0042,0.0025,0.0009,0.9970</t>
-  </si>
-  <si>
-    <t>0.0011,0.9729,0.5930,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9447,0.8901,0.0002</t>
-  </si>
-  <si>
-    <t>0.0051,0.8008,0.7941,0.0019</t>
-  </si>
-  <si>
-    <t>0.0162,0.2153,0.8986,0.0135</t>
-  </si>
-  <si>
-    <t>0.0004,0.9594,0.7667,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.8877,0.7574,0.0008</t>
-  </si>
-  <si>
-    <t>0.9905,0.0041,0.0012,0.0010</t>
-  </si>
-  <si>
-    <t>0.9864,0.0100,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.9898,0.0104,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9920,0.0040,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.9819,0.0158,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.9906,0.0041,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9895,0.0094,0.0012,0.0006</t>
-  </si>
-  <si>
-    <t>0.9822,0.0118,0.0036,0.0010</t>
-  </si>
-  <si>
-    <t>0.9902,0.0031,0.0008,0.0017</t>
-  </si>
-  <si>
-    <t>0.9894,0.0055,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.9880,0.0029,0.0012,0.0025</t>
-  </si>
-  <si>
-    <t>0.9907,0.0024,0.0008,0.0019</t>
-  </si>
-  <si>
-    <t>0.9907,0.0041,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9871,0.0088,0.0023,0.0008</t>
-  </si>
-  <si>
-    <t>0.9911,0.0040,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9950,0.0014,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.0177,0.0076,0.9337,0.0647</t>
-  </si>
-  <si>
-    <t>0.0808,0.0914,0.8590,0.0210</t>
-  </si>
-  <si>
-    <t>0.3067,0.0716,0.1550,0.5438</t>
-  </si>
-  <si>
-    <t>0.1441,0.0065,0.8842,0.0139</t>
-  </si>
-  <si>
-    <t>0.0884,0.9083,0.0254,0.0016</t>
-  </si>
-  <si>
-    <t>0.1136,0.9161,0.0091,0.0011</t>
-  </si>
-  <si>
-    <t>0.3491,0.7674,0.0087,0.0008</t>
-  </si>
-  <si>
-    <t>0.3193,0.7530,0.0141,0.0010</t>
-  </si>
-  <si>
-    <t>0.1090,0.9147,0.0133,0.0014</t>
-  </si>
-  <si>
-    <t>0.0250,0.9736,0.0133,0.0004</t>
-  </si>
-  <si>
-    <t>0.5470,0.5337,0.0202,0.0021</t>
-  </si>
-  <si>
-    <t>0.2607,0.5785,0.2434,0.0197</t>
-  </si>
-  <si>
-    <t>0.1856,0.0165,0.8080,0.0425</t>
-  </si>
-  <si>
-    <t>0.5271,0.2062,0.2684,0.1193</t>
-  </si>
-  <si>
-    <t>0.1943,0.3533,0.4793,0.0103</t>
-  </si>
-  <si>
-    <t>0.6435,0.0526,0.1795,0.1588</t>
-  </si>
-  <si>
-    <t>0.0091,0.9786,0.0502,0.0007</t>
-  </si>
-  <si>
-    <t>0.0023,0.9855,0.0175,0.0076</t>
-  </si>
-  <si>
-    <t>0.0163,0.9664,0.0123,0.0081</t>
-  </si>
-  <si>
-    <t>0.0003,0.9945,0.2433,0.0001</t>
-  </si>
-  <si>
-    <t>0.0752,0.8758,0.0785,0.0012</t>
-  </si>
-  <si>
-    <t>0.8956,0.1381,0.0169,0.0020</t>
-  </si>
-  <si>
-    <t>0.5547,0.5248,0.0264,0.0022</t>
-  </si>
-  <si>
-    <t>0.9569,0.0352,0.0151,0.0029</t>
-  </si>
-  <si>
-    <t>0.9599,0.0096,0.0079,0.0125</t>
-  </si>
-  <si>
-    <t>0.9903,0.0038,0.0007,0.0015</t>
-  </si>
-  <si>
-    <t>0.9702,0.0136,0.0064,0.0034</t>
-  </si>
-  <si>
-    <t>0.9883,0.0051,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.9697,0.0226,0.0086,0.0018</t>
-  </si>
-  <si>
-    <t>0.9807,0.0097,0.0025,0.0027</t>
-  </si>
-  <si>
-    <t>0.9818,0.0067,0.0030,0.0020</t>
-  </si>
-  <si>
-    <t>0.0059,0.2550,0.9497,0.0028</t>
-  </si>
-  <si>
-    <t>0.0026,0.2968,0.9639,0.0003</t>
-  </si>
-  <si>
-    <t>0.0044,0.1771,0.9687,0.0005</t>
-  </si>
-  <si>
-    <t>0.0158,0.2295,0.9171,0.0026</t>
-  </si>
-  <si>
-    <t>0.2785,0.4008,0.3075,0.1748</t>
-  </si>
-  <si>
-    <t>0.6689,0.1406,0.2340,0.0268</t>
-  </si>
-  <si>
-    <t>0.3875,0.0155,0.6770,0.0287</t>
-  </si>
-  <si>
-    <t>0.5227,0.1172,0.4568,0.0181</t>
-  </si>
-  <si>
-    <t>0.0493,0.0113,0.0033,0.9772</t>
-  </si>
-  <si>
-    <t>0.0024,0.0014,0.0003,0.9985</t>
-  </si>
-  <si>
-    <t>0.0096,0.0376,0.0030,0.9897</t>
-  </si>
-  <si>
-    <t>0.0532,0.0034,0.0024,0.9812</t>
-  </si>
-  <si>
-    <t>0.0026,0.8849,0.7980,0.0013</t>
-  </si>
-  <si>
-    <t>0.9753,0.0126,0.0022,0.0043</t>
-  </si>
-  <si>
-    <t>0.7019,0.3819,0.0228,0.0071</t>
-  </si>
-  <si>
-    <t>0.9701,0.0117,0.0054,0.0053</t>
-  </si>
-  <si>
-    <t>0.7958,0.2658,0.0190,0.0023</t>
-  </si>
-  <si>
-    <t>0.9690,0.0144,0.0048,0.0048</t>
-  </si>
-  <si>
-    <t>0.5936,0.0092,0.0197,0.4619</t>
-  </si>
-  <si>
-    <t>0.9678,0.0071,0.0021,0.0116</t>
-  </si>
-  <si>
-    <t>0.0070,0.0248,0.9701,0.0176</t>
-  </si>
-  <si>
-    <t>0.5005,0.0036,0.0048,0.6811</t>
-  </si>
-  <si>
-    <t>0.8804,0.0052,0.0028,0.1277</t>
-  </si>
-  <si>
-    <t>0.3398,0.5790,0.1323,0.0152</t>
-  </si>
-  <si>
-    <t>0.7058,0.1583,0.1891,0.0248</t>
-  </si>
-  <si>
-    <t>0.7526,0.2146,0.0876,0.0120</t>
-  </si>
-  <si>
-    <t>0.3370,0.5520,0.1391,0.0137</t>
-  </si>
-  <si>
-    <t>0.4568,0.4114,0.1561,0.0114</t>
-  </si>
-  <si>
-    <t>0.5102,0.4327,0.1075,0.0090</t>
-  </si>
-  <si>
-    <t>0.9847,0.0059,0.0021,0.0022</t>
-  </si>
-  <si>
-    <t>0.9756,0.0168,0.0043,0.0025</t>
-  </si>
-  <si>
-    <t>0.9841,0.0057,0.0033,0.0020</t>
-  </si>
-  <si>
-    <t>0.9682,0.0126,0.0060,0.0053</t>
-  </si>
-  <si>
-    <t>0.9669,0.0178,0.0059,0.0040</t>
-  </si>
-  <si>
-    <t>0.9767,0.0250,0.0030,0.0012</t>
-  </si>
-  <si>
-    <t>0.9846,0.0060,0.0014,0.0029</t>
-  </si>
-  <si>
-    <t>0.9830,0.0037,0.0007,0.0056</t>
-  </si>
-  <si>
-    <t>0.7276,0.3626,0.0170,0.0016</t>
-  </si>
-  <si>
-    <t>0.8480,0.1726,0.0311,0.0038</t>
-  </si>
-  <si>
-    <t>0.4831,0.6338,0.0128,0.0033</t>
-  </si>
-  <si>
-    <t>0.2726,0.0604,0.7792,0.0069</t>
-  </si>
-  <si>
-    <t>0.9849,0.0110,0.0030,0.0007</t>
-  </si>
-  <si>
-    <t>0.9546,0.0262,0.0177,0.0034</t>
-  </si>
-  <si>
-    <t>0.9784,0.0110,0.0035,0.0029</t>
-  </si>
-  <si>
-    <t>0.8854,0.1442,0.0223,0.0023</t>
-  </si>
-  <si>
-    <t>0.0013,0.0108,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.9348,0.0953,0.0096,0.0014</t>
-  </si>
-  <si>
-    <t>0.0038,0.0027,0.9941,0.0019</t>
-  </si>
-  <si>
-    <t>0.0069,0.0176,0.9768,0.0092</t>
-  </si>
-  <si>
-    <t>0.3032,0.0203,0.7908,0.0128</t>
-  </si>
-  <si>
-    <t>0.0073,0.2654,0.9478,0.0043</t>
-  </si>
-  <si>
-    <t>0.1713,0.0846,0.8130,0.0116</t>
-  </si>
-  <si>
-    <t>0.0193,0.0019,0.9877,0.0015</t>
-  </si>
-  <si>
-    <t>0.0092,0.0161,0.9851,0.0014</t>
-  </si>
-  <si>
-    <t>0.3047,0.0844,0.6966,0.0115</t>
-  </si>
-  <si>
-    <t>0.1044,0.2846,0.6535,0.0096</t>
-  </si>
-  <si>
-    <t>0.3478,0.0405,0.7504,0.0068</t>
-  </si>
-  <si>
-    <t>0.3058,0.1431,0.6017,0.0078</t>
-  </si>
-  <si>
-    <t>0.1569,0.5271,0.3481,0.0232</t>
-  </si>
-  <si>
-    <t>0.1308,0.6155,0.3076,0.0055</t>
-  </si>
-  <si>
-    <t>0.6670,0.0657,0.1939,0.0924</t>
-  </si>
-  <si>
-    <t>0.4147,0.0681,0.6469,0.0114</t>
-  </si>
-  <si>
-    <t>0.1981,0.8251,0.0244,0.0014</t>
-  </si>
-  <si>
-    <t>0.9168,0.1407,0.0068,0.0007</t>
-  </si>
-  <si>
-    <t>0.8709,0.1692,0.0188,0.0033</t>
-  </si>
-  <si>
-    <t>0.9769,0.0238,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9690,0.0366,0.0059,0.0008</t>
-  </si>
-  <si>
-    <t>0.2606,0.2947,0.4928,0.0187</t>
-  </si>
-  <si>
-    <t>0.6493,0.1174,0.1963,0.1003</t>
-  </si>
-  <si>
-    <t>0.4902,0.1162,0.4032,0.1037</t>
-  </si>
-  <si>
-    <t>0.3567,0.0391,0.6978,0.0416</t>
-  </si>
-  <si>
-    <t>0.6060,0.0538,0.2516,0.1205</t>
-  </si>
-  <si>
-    <t>0.0046,0.0113,0.9871,0.0064</t>
-  </si>
-  <si>
-    <t>0.1228,0.1039,0.7665,0.0424</t>
-  </si>
-  <si>
-    <t>0.0130,0.0836,0.9583,0.0053</t>
-  </si>
-  <si>
-    <t>0.0899,0.1057,0.8015,0.0470</t>
-  </si>
-  <si>
-    <t>0.0259,0.0661,0.9246,0.0192</t>
-  </si>
-  <si>
-    <t>0.9918,0.0043,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9571,0.0568,0.0092,0.0011</t>
-  </si>
-  <si>
-    <t>0.9827,0.0133,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.9815,0.0096,0.0034,0.0017</t>
-  </si>
-  <si>
-    <t>0.9935,0.0031,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9913,0.0070,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9875,0.0069,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9836,0.0079,0.0030,0.0020</t>
-  </si>
-  <si>
-    <t>0.0447,0.0357,0.9411,0.0048</t>
-  </si>
-  <si>
-    <t>0.6331,0.2207,0.1944,0.0097</t>
-  </si>
-  <si>
-    <t>0.9311,0.0229,0.0439,0.0071</t>
-  </si>
-  <si>
-    <t>0.0141,0.0045,0.9863,0.0022</t>
-  </si>
-  <si>
-    <t>0.0029,0.0058,0.9920,0.0037</t>
-  </si>
-  <si>
-    <t>0.0116,0.0076,0.9860,0.0014</t>
-  </si>
-  <si>
-    <t>0.0045,0.0037,0.9932,0.0020</t>
-  </si>
-  <si>
-    <t>0.0330,0.0061,0.9609,0.0110</t>
-  </si>
-  <si>
-    <t>0.0074,0.0148,0.9810,0.0044</t>
-  </si>
-  <si>
-    <t>0.0126,0.0140,0.9733,0.0061</t>
-  </si>
-  <si>
-    <t>0.1336,0.3261,0.5828,0.0123</t>
-  </si>
-  <si>
-    <t>0.3123,0.0684,0.6739,0.0517</t>
-  </si>
-  <si>
-    <t>0.5113,0.0255,0.3179,0.1171</t>
-  </si>
-  <si>
-    <t>0.6316,0.0148,0.1556,0.1243</t>
-  </si>
-  <si>
-    <t>0.9914,0.0033,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9926,0.0070,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9866,0.0116,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.9889,0.0073,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.9929,0.0023,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9893,0.0061,0.0012,0.0009</t>
-  </si>
-  <si>
-    <t>0.9912,0.0067,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9933,0.0025,0.0006,0.0009</t>
-  </si>
-  <si>
-    <t>0.0604,0.0158,0.9378,0.0066</t>
-  </si>
-  <si>
-    <t>0.0092,0.0357,0.9696,0.0108</t>
-  </si>
-  <si>
-    <t>0.0258,0.1791,0.9019,0.0165</t>
-  </si>
-  <si>
-    <t>0.1537,0.0286,0.6681,0.2088</t>
-  </si>
-  <si>
-    <t>0.0239,0.0112,0.9594,0.0140</t>
-  </si>
-  <si>
-    <t>0.0846,0.0194,0.8352,0.0962</t>
-  </si>
-  <si>
-    <t>0.0418,0.1161,0.8998,0.0065</t>
-  </si>
-  <si>
-    <t>0.0115,0.0023,0.3870,0.7589</t>
-  </si>
-  <si>
-    <t>0.3731,0.0094,0.0026,0.8038</t>
-  </si>
-  <si>
-    <t>0.0143,0.0030,0.0035,0.9909</t>
-  </si>
-  <si>
-    <t>0.0222,0.0190,0.0018,0.9859</t>
-  </si>
-  <si>
-    <t>0.0167,0.0090,0.0018,0.9903</t>
-  </si>
-  <si>
-    <t>0.0069,0.0113,0.0012,0.9942</t>
-  </si>
-  <si>
-    <t>0.6292,0.0303,0.0533,0.3093</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8219,0.0338,0.0126,0.1143</t>
+  </si>
+  <si>
+    <t>0.0821,0.0099,0.0085,0.9588</t>
+  </si>
+  <si>
+    <t>0.5737,0.0520,0.0152,0.4108</t>
+  </si>
+  <si>
+    <t>0.1080,0.0128,0.0017,0.9563</t>
+  </si>
+  <si>
+    <t>0.9915,0.0039,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9914,0.0037,0.0006,0.0012</t>
+  </si>
+  <si>
+    <t>0.9873,0.0073,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9910,0.0029,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9906,0.0075,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.9902,0.0029,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.9863,0.0053,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.9872,0.0065,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.6255,0.0514,0.3415,0.0533</t>
+  </si>
+  <si>
+    <t>0.4218,0.0533,0.6566,0.0224</t>
+  </si>
+  <si>
+    <t>0.4390,0.0911,0.5700,0.0150</t>
+  </si>
+  <si>
+    <t>0.1701,0.2457,0.6432,0.0135</t>
+  </si>
+  <si>
+    <t>0.8480,0.0584,0.0639,0.0262</t>
+  </si>
+  <si>
+    <t>0.0095,0.9870,0.0073,0.0004</t>
+  </si>
+  <si>
+    <t>0.0247,0.9726,0.0174,0.0004</t>
+  </si>
+  <si>
+    <t>0.4692,0.5533,0.0369,0.0019</t>
+  </si>
+  <si>
+    <t>0.0340,0.9619,0.0232,0.0008</t>
+  </si>
+  <si>
+    <t>0.0090,0.9829,0.0175,0.0002</t>
+  </si>
+  <si>
+    <t>0.6279,0.0596,0.1609,0.1187</t>
+  </si>
+  <si>
+    <t>0.3925,0.1203,0.5359,0.0733</t>
+  </si>
+  <si>
+    <t>0.0211,0.0365,0.9543,0.0106</t>
+  </si>
+  <si>
+    <t>0.0959,0.0097,0.9252,0.0106</t>
+  </si>
+  <si>
+    <t>0.2631,0.0126,0.7598,0.0398</t>
+  </si>
+  <si>
+    <t>0.1595,0.0096,0.5721,0.2124</t>
+  </si>
+  <si>
+    <t>0.0366,0.0083,0.9413,0.0280</t>
+  </si>
+  <si>
+    <t>0.3562,0.7533,0.0084,0.0027</t>
+  </si>
+  <si>
+    <t>0.3535,0.0607,0.6901,0.0213</t>
+  </si>
+  <si>
+    <t>0.0041,0.0253,0.9880,0.0024</t>
+  </si>
+  <si>
+    <t>0.0090,0.9263,0.3621,0.0014</t>
+  </si>
+  <si>
+    <t>0.8420,0.0815,0.0128,0.0541</t>
+  </si>
+  <si>
+    <t>0.5822,0.0558,0.4294,0.0389</t>
+  </si>
+  <si>
+    <t>0.8376,0.1960,0.0277,0.0036</t>
+  </si>
+  <si>
+    <t>0.0845,0.8697,0.0882,0.0030</t>
+  </si>
+  <si>
+    <t>0.0073,0.9473,0.3245,0.0031</t>
+  </si>
+  <si>
+    <t>0.0287,0.4122,0.8268,0.0187</t>
+  </si>
+  <si>
+    <t>0.0581,0.0387,0.9155,0.0108</t>
+  </si>
+  <si>
+    <t>0.0928,0.0362,0.4087,0.5190</t>
+  </si>
+  <si>
+    <t>0.0088,0.7414,0.7977,0.0029</t>
+  </si>
+  <si>
+    <t>0.0012,0.9895,0.1178,0.0003</t>
+  </si>
+  <si>
+    <t>0.0251,0.1369,0.9207,0.0046</t>
+  </si>
+  <si>
+    <t>0.0133,0.6477,0.0034,0.8545</t>
+  </si>
+  <si>
+    <t>0.0037,0.9862,0.0567,0.0009</t>
+  </si>
+  <si>
+    <t>0.0041,0.9766,0.1558,0.0007</t>
+  </si>
+  <si>
+    <t>0.0023,0.9822,0.2751,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.8361,0.8544,0.0011</t>
+  </si>
+  <si>
+    <t>0.0026,0.1282,0.9784,0.0018</t>
+  </si>
+  <si>
+    <t>0.2694,0.0270,0.7672,0.0267</t>
+  </si>
+  <si>
+    <t>0.0884,0.0119,0.8962,0.0308</t>
+  </si>
+  <si>
+    <t>0.0160,0.0270,0.9396,0.0486</t>
+  </si>
+  <si>
+    <t>0.0270,0.0444,0.9354,0.0178</t>
+  </si>
+  <si>
+    <t>0.9713,0.0309,0.0052,0.0012</t>
+  </si>
+  <si>
+    <t>0.9596,0.0475,0.0066,0.0022</t>
+  </si>
+  <si>
+    <t>0.9829,0.0084,0.0029,0.0018</t>
+  </si>
+  <si>
+    <t>0.0190,0.0968,0.9579,0.0029</t>
+  </si>
+  <si>
+    <t>0.9776,0.0167,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.9898,0.0042,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9729,0.0164,0.0052,0.0030</t>
+  </si>
+  <si>
+    <t>0.0008,0.9409,0.8238,0.0005</t>
+  </si>
+  <si>
+    <t>0.0012,0.0088,0.9951,0.0010</t>
+  </si>
+  <si>
+    <t>0.0042,0.0219,0.9802,0.0076</t>
+  </si>
+  <si>
+    <t>0.0011,0.9312,0.8168,0.0005</t>
+  </si>
+  <si>
+    <t>0.0048,0.0167,0.9804,0.0083</t>
+  </si>
+  <si>
+    <t>0.0177,0.9670,0.0405,0.0015</t>
+  </si>
+  <si>
+    <t>0.0029,0.9958,0.0044,0.0001</t>
+  </si>
+  <si>
+    <t>0.7795,0.0806,0.1758,0.0206</t>
+  </si>
+  <si>
+    <t>0.5886,0.3369,0.1242,0.0085</t>
+  </si>
+  <si>
+    <t>0.0094,0.0351,0.9792,0.0037</t>
+  </si>
+  <si>
+    <t>0.0008,0.9153,0.8224,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.7831,0.8930,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9860,0.5494,0.0001</t>
+  </si>
+  <si>
+    <t>0.0062,0.8052,0.7832,0.0033</t>
+  </si>
+  <si>
+    <t>0.1010,0.0274,0.0284,0.9206</t>
+  </si>
+  <si>
+    <t>0.0053,0.0064,0.0007,0.9965</t>
+  </si>
+  <si>
+    <t>0.0033,0.0157,0.0004,0.9971</t>
+  </si>
+  <si>
+    <t>0.0212,0.0228,0.0034,0.9855</t>
+  </si>
+  <si>
+    <t>0.0492,0.0113,0.0123,0.9654</t>
+  </si>
+  <si>
+    <t>0.0046,0.0191,0.0019,0.9942</t>
+  </si>
+  <si>
+    <t>0.0009,0.9846,0.4016,0.0002</t>
+  </si>
+  <si>
+    <t>0.0108,0.3337,0.9155,0.0046</t>
+  </si>
+  <si>
+    <t>0.0102,0.8393,0.6210,0.0041</t>
+  </si>
+  <si>
+    <t>0.0066,0.3811,0.9209,0.0032</t>
+  </si>
+  <si>
+    <t>0.0015,0.7195,0.9105,0.0003</t>
+  </si>
+  <si>
+    <t>0.0032,0.8999,0.7000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9871,0.0087,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.9893,0.0054,0.0013,0.0012</t>
+  </si>
+  <si>
+    <t>0.9774,0.0366,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.9684,0.0212,0.0057,0.0030</t>
+  </si>
+  <si>
+    <t>0.9899,0.0053,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9871,0.0156,0.0015,0.0005</t>
+  </si>
+  <si>
+    <t>0.9881,0.0085,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9857,0.0114,0.0016,0.0009</t>
+  </si>
+  <si>
+    <t>0.9926,0.0018,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9940,0.0014,0.0004,0.0012</t>
+  </si>
+  <si>
+    <t>0.9834,0.0080,0.0026,0.0020</t>
+  </si>
+  <si>
+    <t>0.9916,0.0022,0.0004,0.0020</t>
+  </si>
+  <si>
+    <t>0.9887,0.0057,0.0012,0.0011</t>
+  </si>
+  <si>
+    <t>0.9911,0.0058,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9941,0.0030,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9900,0.0052,0.0009,0.0010</t>
+  </si>
+  <si>
+    <t>0.0090,0.0052,0.9533,0.0599</t>
+  </si>
+  <si>
+    <t>0.1614,0.0412,0.8469,0.0110</t>
+  </si>
+  <si>
+    <t>0.5462,0.0176,0.2841,0.0968</t>
+  </si>
+  <si>
+    <t>0.2334,0.0199,0.8306,0.0086</t>
+  </si>
+  <si>
+    <t>0.0875,0.9153,0.0226,0.0017</t>
+  </si>
+  <si>
+    <t>0.0256,0.9636,0.0168,0.0007</t>
+  </si>
+  <si>
+    <t>0.2350,0.8252,0.0139,0.0011</t>
+  </si>
+  <si>
+    <t>0.1488,0.8756,0.0132,0.0006</t>
+  </si>
+  <si>
+    <t>0.0618,0.9416,0.0139,0.0018</t>
+  </si>
+  <si>
+    <t>0.0100,0.9864,0.0076,0.0003</t>
+  </si>
+  <si>
+    <t>0.6654,0.3959,0.0190,0.0013</t>
+  </si>
+  <si>
+    <t>0.5180,0.2720,0.2802,0.0311</t>
+  </si>
+  <si>
+    <t>0.4079,0.0639,0.6152,0.0412</t>
+  </si>
+  <si>
+    <t>0.3065,0.4728,0.2419,0.0154</t>
+  </si>
+  <si>
+    <t>0.2091,0.2731,0.5598,0.0217</t>
+  </si>
+  <si>
+    <t>0.6373,0.2210,0.1111,0.0873</t>
+  </si>
+  <si>
+    <t>0.0037,0.9807,0.1549,0.0010</t>
+  </si>
+  <si>
+    <t>0.0021,0.9870,0.0582,0.0017</t>
+  </si>
+  <si>
+    <t>0.1561,0.7541,0.1345,0.0196</t>
+  </si>
+  <si>
+    <t>0.0006,0.9884,0.4157,0.0002</t>
+  </si>
+  <si>
+    <t>0.0288,0.9293,0.1057,0.0008</t>
+  </si>
+  <si>
+    <t>0.6683,0.3208,0.0610,0.0026</t>
+  </si>
+  <si>
+    <t>0.7152,0.3313,0.0228,0.0012</t>
+  </si>
+  <si>
+    <t>0.9801,0.0121,0.0040,0.0015</t>
+  </si>
+  <si>
+    <t>0.9874,0.0052,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.9843,0.0027,0.0016,0.0051</t>
+  </si>
+  <si>
+    <t>0.9728,0.0153,0.0081,0.0017</t>
+  </si>
+  <si>
+    <t>0.9817,0.0140,0.0036,0.0009</t>
+  </si>
+  <si>
+    <t>0.9802,0.0127,0.0035,0.0016</t>
+  </si>
+  <si>
+    <t>0.9831,0.0069,0.0025,0.0023</t>
+  </si>
+  <si>
+    <t>0.9805,0.0075,0.0071,0.0015</t>
+  </si>
+  <si>
+    <t>0.0127,0.2014,0.9363,0.0039</t>
+  </si>
+  <si>
+    <t>0.0049,0.6012,0.8817,0.0014</t>
+  </si>
+  <si>
+    <t>0.0076,0.1176,0.9636,0.0018</t>
+  </si>
+  <si>
+    <t>0.0303,0.3955,0.8100,0.0095</t>
+  </si>
+  <si>
+    <t>0.6030,0.2571,0.1146,0.0850</t>
+  </si>
+  <si>
+    <t>0.6717,0.0719,0.2164,0.0844</t>
+  </si>
+  <si>
+    <t>0.4219,0.0274,0.5573,0.0647</t>
+  </si>
+  <si>
+    <t>0.6007,0.1483,0.1653,0.1338</t>
+  </si>
+  <si>
+    <t>0.0193,0.0132,0.0020,0.9891</t>
+  </si>
+  <si>
+    <t>0.0036,0.0017,0.0006,0.9976</t>
+  </si>
+  <si>
+    <t>0.0160,0.0191,0.0016,0.9902</t>
+  </si>
+  <si>
+    <t>0.0202,0.0065,0.0013,0.9906</t>
+  </si>
+  <si>
+    <t>0.0005,0.9702,0.7170,0.0002</t>
+  </si>
+  <si>
+    <t>0.9863,0.0096,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.1810,0.8432,0.0176,0.0020</t>
+  </si>
+  <si>
+    <t>0.9517,0.0099,0.0012,0.0259</t>
+  </si>
+  <si>
+    <t>0.9303,0.0814,0.0172,0.0026</t>
+  </si>
+  <si>
+    <t>0.9569,0.0110,0.0052,0.0146</t>
+  </si>
+  <si>
+    <t>0.8019,0.0227,0.0526,0.0998</t>
+  </si>
+  <si>
+    <t>0.9688,0.0083,0.0028,0.0111</t>
+  </si>
+  <si>
+    <t>0.0075,0.0373,0.9195,0.0818</t>
+  </si>
+  <si>
+    <t>0.5082,0.0050,0.0050,0.6697</t>
+  </si>
+  <si>
+    <t>0.9233,0.0077,0.0041,0.0570</t>
+  </si>
+  <si>
+    <t>0.2764,0.7022,0.0429,0.0413</t>
+  </si>
+  <si>
+    <t>0.6620,0.2535,0.1671,0.0211</t>
+  </si>
+  <si>
+    <t>0.9069,0.0446,0.0383,0.0113</t>
+  </si>
+  <si>
+    <t>0.0372,0.9229,0.0839,0.0062</t>
+  </si>
+  <si>
+    <t>0.1924,0.6989,0.1769,0.0111</t>
+  </si>
+  <si>
+    <t>0.4956,0.4082,0.1389,0.0094</t>
+  </si>
+  <si>
+    <t>0.9839,0.0061,0.0030,0.0022</t>
+  </si>
+  <si>
+    <t>0.9807,0.0103,0.0026,0.0027</t>
+  </si>
+  <si>
+    <t>0.9817,0.0054,0.0009,0.0060</t>
+  </si>
+  <si>
+    <t>0.9753,0.0127,0.0049,0.0028</t>
+  </si>
+  <si>
+    <t>0.9806,0.0097,0.0025,0.0024</t>
+  </si>
+  <si>
+    <t>0.9716,0.0175,0.0048,0.0028</t>
+  </si>
+  <si>
+    <t>0.9846,0.0097,0.0011,0.0019</t>
+  </si>
+  <si>
+    <t>0.9861,0.0028,0.0008,0.0044</t>
+  </si>
+  <si>
+    <t>0.7566,0.3442,0.0139,0.0014</t>
+  </si>
+  <si>
+    <t>0.6520,0.4351,0.0179,0.0023</t>
+  </si>
+  <si>
+    <t>0.7201,0.3280,0.0330,0.0035</t>
+  </si>
+  <si>
+    <t>0.2414,0.0617,0.8188,0.0069</t>
+  </si>
+  <si>
+    <t>0.9556,0.0482,0.0105,0.0014</t>
+  </si>
+  <si>
+    <t>0.9227,0.0687,0.0249,0.0046</t>
+  </si>
+  <si>
+    <t>0.9869,0.0107,0.0020,0.0005</t>
+  </si>
+  <si>
+    <t>0.9242,0.0710,0.0117,0.0059</t>
+  </si>
+  <si>
+    <t>0.0022,0.0050,0.9967,0.0005</t>
+  </si>
+  <si>
+    <t>0.9457,0.0381,0.0160,0.0034</t>
+  </si>
+  <si>
+    <t>0.0047,0.0043,0.9883,0.0073</t>
+  </si>
+  <si>
+    <t>0.0263,0.0385,0.9657,0.0023</t>
+  </si>
+  <si>
+    <t>0.3723,0.0672,0.6726,0.0170</t>
+  </si>
+  <si>
+    <t>0.0079,0.6435,0.8325,0.0017</t>
+  </si>
+  <si>
+    <t>0.0153,0.0041,0.9887,0.0008</t>
+  </si>
+  <si>
+    <t>0.1053,0.0037,0.9376,0.0054</t>
+  </si>
+  <si>
+    <t>0.0168,0.0044,0.9758,0.0132</t>
+  </si>
+  <si>
+    <t>0.2221,0.2319,0.6125,0.0258</t>
+  </si>
+  <si>
+    <t>0.0923,0.0792,0.8657,0.0071</t>
+  </si>
+  <si>
+    <t>0.7031,0.0530,0.1893,0.0745</t>
+  </si>
+  <si>
+    <t>0.3879,0.1613,0.5263,0.0308</t>
+  </si>
+  <si>
+    <t>0.1883,0.5746,0.3049,0.0128</t>
+  </si>
+  <si>
+    <t>0.4360,0.3313,0.3056,0.0647</t>
+  </si>
+  <si>
+    <t>0.4012,0.0980,0.5902,0.0203</t>
+  </si>
+  <si>
+    <t>0.4624,0.1232,0.4701,0.0151</t>
+  </si>
+  <si>
+    <t>0.8123,0.3081,0.0118,0.0019</t>
+  </si>
+  <si>
+    <t>0.3940,0.6966,0.0117,0.0008</t>
+  </si>
+  <si>
+    <t>0.9614,0.0620,0.0046,0.0011</t>
+  </si>
+  <si>
+    <t>0.9768,0.0351,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.9714,0.0366,0.0045,0.0008</t>
+  </si>
+  <si>
+    <t>0.5452,0.0701,0.4427,0.0303</t>
+  </si>
+  <si>
+    <t>0.5537,0.0263,0.5592,0.0133</t>
+  </si>
+  <si>
+    <t>0.5175,0.1176,0.1154,0.2816</t>
+  </si>
+  <si>
+    <t>0.4918,0.0649,0.4998,0.0518</t>
+  </si>
+  <si>
+    <t>0.7089,0.0197,0.1172,0.1087</t>
+  </si>
+  <si>
+    <t>0.0450,0.0420,0.9303,0.0243</t>
+  </si>
+  <si>
+    <t>0.1394,0.1418,0.7559,0.0486</t>
+  </si>
+  <si>
+    <t>0.0394,0.2068,0.8818,0.0064</t>
+  </si>
+  <si>
+    <t>0.0887,0.0790,0.8101,0.0387</t>
+  </si>
+  <si>
+    <t>0.0223,0.2321,0.7460,0.0880</t>
+  </si>
+  <si>
+    <t>0.9846,0.0069,0.0023,0.0019</t>
+  </si>
+  <si>
+    <t>0.9871,0.0078,0.0020,0.0010</t>
+  </si>
+  <si>
+    <t>0.9891,0.0062,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.9880,0.0050,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.9897,0.0059,0.0010,0.0009</t>
+  </si>
+  <si>
+    <t>0.9866,0.0073,0.0022,0.0011</t>
+  </si>
+  <si>
+    <t>0.9881,0.0048,0.0020,0.0012</t>
+  </si>
+  <si>
+    <t>0.9839,0.0084,0.0031,0.0016</t>
+  </si>
+  <si>
+    <t>0.0562,0.0409,0.9201,0.0064</t>
+  </si>
+  <si>
+    <t>0.2389,0.1216,0.6882,0.0068</t>
+  </si>
+  <si>
+    <t>0.8955,0.0437,0.0506,0.0171</t>
+  </si>
+  <si>
+    <t>0.0064,0.0630,0.9731,0.0031</t>
+  </si>
+  <si>
+    <t>0.0037,0.0399,0.9795,0.0076</t>
+  </si>
+  <si>
+    <t>0.0303,0.0267,0.9487,0.0126</t>
+  </si>
+  <si>
+    <t>0.0008,0.0020,0.9985,0.0003</t>
+  </si>
+  <si>
+    <t>0.1066,0.0227,0.8932,0.0095</t>
+  </si>
+  <si>
+    <t>0.0019,0.0131,0.9923,0.0018</t>
+  </si>
+  <si>
+    <t>0.0199,0.0314,0.9439,0.0225</t>
+  </si>
+  <si>
+    <t>0.3313,0.0748,0.6688,0.0213</t>
+  </si>
+  <si>
+    <t>0.5098,0.0425,0.4384,0.0701</t>
+  </si>
+  <si>
+    <t>0.4753,0.0213,0.5167,0.0609</t>
+  </si>
+  <si>
+    <t>0.6137,0.0603,0.1984,0.1364</t>
+  </si>
+  <si>
+    <t>0.9918,0.0052,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9797,0.0132,0.0055,0.0012</t>
+  </si>
+  <si>
+    <t>0.9804,0.0192,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9883,0.0086,0.0016,0.0007</t>
+  </si>
+  <si>
+    <t>0.9930,0.0021,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9786,0.0237,0.0036,0.0008</t>
+  </si>
+  <si>
+    <t>0.9919,0.0032,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9841,0.0098,0.0017,0.0017</t>
+  </si>
+  <si>
+    <t>0.0111,0.0506,0.9757,0.0012</t>
+  </si>
+  <si>
+    <t>0.0115,0.1086,0.9543,0.0075</t>
+  </si>
+  <si>
+    <t>0.0174,0.4348,0.8450,0.0049</t>
+  </si>
+  <si>
+    <t>0.2124,0.0534,0.7691,0.0356</t>
+  </si>
+  <si>
+    <t>0.0199,0.0162,0.9700,0.0062</t>
+  </si>
+  <si>
+    <t>0.2548,0.1037,0.4027,0.3864</t>
+  </si>
+  <si>
+    <t>0.1370,0.1787,0.7241,0.0432</t>
+  </si>
+  <si>
+    <t>0.1309,0.0309,0.5285,0.3417</t>
+  </si>
+  <si>
+    <t>0.1686,0.0197,0.0056,0.9198</t>
+  </si>
+  <si>
+    <t>0.0171,0.3254,0.0034,0.9499</t>
+  </si>
+  <si>
+    <t>0.0246,0.0267,0.0043,0.9810</t>
+  </si>
+  <si>
+    <t>0.0038,0.0048,0.0003,0.9977</t>
+  </si>
+  <si>
+    <t>0.0010,0.0096,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.6289,0.2020,0.0454,0.1309</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2189,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>260</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2539,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3620,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4219,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4221,10 +4233,10 @@
         <v>259</v>
       </c>
       <c r="C164" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4541,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4656,7 @@
         <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5454,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
